--- a/org_structure.xlsx
+++ b/org_structure.xlsx
@@ -695,11 +695,7 @@
           <t>Активний</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Зубрицька Олександра</t>
-        </is>
-      </c>
+      <c r="G6" s="4" t="n"/>
     </row>
     <row r="7" ht="19" customHeight="1" s="14">
       <c r="A7" s="5" t="inlineStr">
@@ -761,11 +757,7 @@
           <t>Активний</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Віталій</t>
-        </is>
-      </c>
+      <c r="G8" s="4" t="n"/>
     </row>
     <row r="9" ht="19" customHeight="1" s="14">
       <c r="A9" s="7" t="inlineStr">
@@ -984,11 +976,7 @@
           <t>Активний</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Євген</t>
-        </is>
-      </c>
+      <c r="G15" s="10" t="n"/>
     </row>
     <row r="16" ht="19" customHeight="1" s="14">
       <c r="A16" s="9" t="inlineStr">
@@ -1112,11 +1100,7 @@
           <t>Активний</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Щуліпенко Зоряна</t>
-        </is>
-      </c>
+      <c r="G19" s="10" t="n"/>
     </row>
     <row r="20" ht="19" customHeight="1" s="14">
       <c r="A20" s="9" t="inlineStr">
@@ -1364,11 +1348,7 @@
           <t>Активний</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
-        <is>
-          <t>Жолудь Максим</t>
-        </is>
-      </c>
+      <c r="G27" s="10" t="n"/>
     </row>
     <row r="28" ht="19" customHeight="1" s="14">
       <c r="A28" s="5" t="inlineStr">
@@ -1868,11 +1848,7 @@
           <t>Активний</t>
         </is>
       </c>
-      <c r="G43" s="10" t="inlineStr">
-        <is>
-          <t>Стріляний Олександр</t>
-        </is>
-      </c>
+      <c r="G43" s="10" t="n"/>
     </row>
     <row r="44" ht="19" customHeight="1" s="14">
       <c r="A44" s="7" t="inlineStr">
@@ -1996,11 +1972,7 @@
           <t>Активний</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>Бруновський Михайло</t>
-        </is>
-      </c>
+      <c r="G47" s="4" t="n"/>
     </row>
     <row r="48" ht="19" customHeight="1" s="14">
       <c r="A48" s="7" t="inlineStr">
